--- a/Data Science/Analyst-to-Architect/companion/ch10/ch10_tracker_check.xlsx
+++ b/Data Science/Analyst-to-Architect/companion/ch10/ch10_tracker_check.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reps" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customers" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Targets" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Reps" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Data" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Customers" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Products" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Targets" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -199,13 +199,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -229,7 +229,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -259,14 +259,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -313,7 +313,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>8</col>
@@ -328,9 +328,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -705,7 +705,7 @@
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>SUMIFS(Data!$J$2:$J$331,Data!$B$2:$B$331,"&gt;="&amp;A5,Data!$B$2:$B$331,"&lt;="&amp;EOMONTH(A5,0),Data!$H$2:$H$331,"&lt;&gt;Cancelled")</f>
+        <f>SUMIFS(Data!$J$2:$J$331,Data!$K$2:$K$331,A5,Data!$H$2:$H$331,"&lt;&gt;Cancelled")</f>
         <v/>
       </c>
       <c r="E5" s="6">
@@ -732,7 +732,7 @@
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>SUMIFS(Data!$J$2:$J$331,Data!$B$2:$B$331,"&gt;="&amp;A6,Data!$B$2:$B$331,"&lt;="&amp;EOMONTH(A6,0),Data!$H$2:$H$331,"&lt;&gt;Cancelled")</f>
+        <f>SUMIFS(Data!$J$2:$J$331,Data!$K$2:$K$331,A6,Data!$H$2:$H$331,"&lt;&gt;Cancelled")</f>
         <v/>
       </c>
       <c r="E6" s="6">
@@ -762,7 +762,7 @@
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>SUMIFS(Data!$J$2:$J$331,Data!$B$2:$B$331,"&gt;="&amp;A7,Data!$B$2:$B$331,"&lt;="&amp;EOMONTH(A7,0),Data!$H$2:$H$331,"&lt;&gt;Cancelled")</f>
+        <f>SUMIFS(Data!$J$2:$J$331,Data!$K$2:$K$331,A7,Data!$H$2:$H$331,"&lt;&gt;Cancelled")</f>
         <v/>
       </c>
       <c r="E7" s="6">
@@ -792,7 +792,7 @@
         <v/>
       </c>
       <c r="D8" s="5">
-        <f>SUMIFS(Data!$J$2:$J$331,Data!$B$2:$B$331,"&gt;="&amp;A8,Data!$B$2:$B$331,"&lt;="&amp;EOMONTH(A8,0),Data!$H$2:$H$331,"&lt;&gt;Cancelled")</f>
+        <f>SUMIFS(Data!$J$2:$J$331,Data!$K$2:$K$331,A8,Data!$H$2:$H$331,"&lt;&gt;Cancelled")</f>
         <v/>
       </c>
       <c r="E8" s="6">
@@ -822,7 +822,7 @@
         <v/>
       </c>
       <c r="D9" s="5">
-        <f>SUMIFS(Data!$J$2:$J$331,Data!$B$2:$B$331,"&gt;="&amp;A9,Data!$B$2:$B$331,"&lt;="&amp;EOMONTH(A9,0),Data!$H$2:$H$331,"&lt;&gt;Cancelled")</f>
+        <f>SUMIFS(Data!$J$2:$J$331,Data!$K$2:$K$331,A9,Data!$H$2:$H$331,"&lt;&gt;Cancelled")</f>
         <v/>
       </c>
       <c r="E9" s="6">
@@ -852,7 +852,7 @@
         <v/>
       </c>
       <c r="D10" s="5">
-        <f>SUMIFS(Data!$J$2:$J$331,Data!$B$2:$B$331,"&gt;="&amp;A10,Data!$B$2:$B$331,"&lt;="&amp;EOMONTH(A10,0),Data!$H$2:$H$331,"&lt;&gt;Cancelled")</f>
+        <f>SUMIFS(Data!$J$2:$J$331,Data!$K$2:$K$331,A10,Data!$H$2:$H$331,"&lt;&gt;Cancelled")</f>
         <v/>
       </c>
       <c r="E10" s="6">
@@ -882,7 +882,7 @@
         <v/>
       </c>
       <c r="D11" s="5">
-        <f>SUMIFS(Data!$J$2:$J$331,Data!$B$2:$B$331,"&gt;="&amp;A11,Data!$B$2:$B$331,"&lt;="&amp;EOMONTH(A11,0),Data!$H$2:$H$331,"&lt;&gt;Cancelled")</f>
+        <f>SUMIFS(Data!$J$2:$J$331,Data!$K$2:$K$331,A11,Data!$H$2:$H$331,"&lt;&gt;Cancelled")</f>
         <v/>
       </c>
       <c r="E11" s="6">
@@ -912,7 +912,7 @@
         <v/>
       </c>
       <c r="D12" s="5">
-        <f>SUMIFS(Data!$J$2:$J$331,Data!$B$2:$B$331,"&gt;="&amp;A12,Data!$B$2:$B$331,"&lt;="&amp;EOMONTH(A12,0),Data!$H$2:$H$331,"&lt;&gt;Cancelled")</f>
+        <f>SUMIFS(Data!$J$2:$J$331,Data!$K$2:$K$331,A12,Data!$H$2:$H$331,"&lt;&gt;Cancelled")</f>
         <v/>
       </c>
       <c r="E12" s="6">
@@ -942,7 +942,7 @@
         <v/>
       </c>
       <c r="D13" s="5">
-        <f>SUMIFS(Data!$J$2:$J$331,Data!$B$2:$B$331,"&gt;="&amp;A13,Data!$B$2:$B$331,"&lt;="&amp;EOMONTH(A13,0),Data!$H$2:$H$331,"&lt;&gt;Cancelled")</f>
+        <f>SUMIFS(Data!$J$2:$J$331,Data!$K$2:$K$331,A13,Data!$H$2:$H$331,"&lt;&gt;Cancelled")</f>
         <v/>
       </c>
       <c r="E13" s="6">
@@ -972,7 +972,7 @@
         <v/>
       </c>
       <c r="D14" s="5">
-        <f>SUMIFS(Data!$J$2:$J$331,Data!$B$2:$B$331,"&gt;="&amp;A14,Data!$B$2:$B$331,"&lt;="&amp;EOMONTH(A14,0),Data!$H$2:$H$331,"&lt;&gt;Cancelled")</f>
+        <f>SUMIFS(Data!$J$2:$J$331,Data!$K$2:$K$331,A14,Data!$H$2:$H$331,"&lt;&gt;Cancelled")</f>
         <v/>
       </c>
       <c r="E14" s="6">
@@ -1002,7 +1002,7 @@
         <v/>
       </c>
       <c r="D15" s="5">
-        <f>SUMIFS(Data!$J$2:$J$331,Data!$B$2:$B$331,"&gt;="&amp;A15,Data!$B$2:$B$331,"&lt;="&amp;EOMONTH(A15,0),Data!$H$2:$H$331,"&lt;&gt;Cancelled")</f>
+        <f>SUMIFS(Data!$J$2:$J$331,Data!$K$2:$K$331,A15,Data!$H$2:$H$331,"&lt;&gt;Cancelled")</f>
         <v/>
       </c>
       <c r="E15" s="6">
@@ -1032,7 +1032,7 @@
         <v/>
       </c>
       <c r="D16" s="5">
-        <f>SUMIFS(Data!$J$2:$J$331,Data!$B$2:$B$331,"&gt;="&amp;A16,Data!$B$2:$B$331,"&lt;="&amp;EOMONTH(A16,0),Data!$H$2:$H$331,"&lt;&gt;Cancelled")</f>
+        <f>SUMIFS(Data!$J$2:$J$331,Data!$K$2:$K$331,A16,Data!$H$2:$H$331,"&lt;&gt;Cancelled")</f>
         <v/>
       </c>
       <c r="E16" s="6">
